--- a/output/pdf_financials_xlsx/FORT.xlsx
+++ b/output/pdf_financials_xlsx/FORT.xlsx
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
     </row>
     <row r="93">
@@ -5090,7 +5090,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -7634,7 +7638,7 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.36</v>
+        <v>-0.36</v>
       </c>
       <c r="J80" s="5" t="n">
         <v>-5.83</v>

--- a/output/pdf_financials_xlsx/FORT.xlsx
+++ b/output/pdf_financials_xlsx/FORT.xlsx
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.000869</v>
+        <v>0.003369</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>0.089365</v>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.000869</v>
+        <v>-0.003369</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-0.089365</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.006511</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.008756</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1115,10 +1115,10 @@
         <v>-0.10767</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.048098</v>
+        <v>-0.041587</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-5.83</v>
+        <v>-5.821244</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-5.83</v>
@@ -1165,10 +1165,10 @@
         <v>-0.10767</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.048098</v>
+        <v>-0.041587</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.83</v>
+        <v>-5.821244</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-5.83</v>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-353.5476046088538</v>
+        <v>-353.0166161309885</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-540.3151065801668</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -10356,14 +10356,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>-0.003369</v>
+        <v>0.003369</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>-0.089365</v>
+        <v>0.089365</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FORT.xlsx
+++ b/output/pdf_financials_xlsx/FORT.xlsx
@@ -1143,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="29">
@@ -1168,10 +1168,10 @@
         <v>-0.041587</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-5.821244</v>
+        <v>-5.763244</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.83</v>
+        <v>-5.736</v>
       </c>
     </row>
     <row r="30">
@@ -1201,10 +1201,10 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-353.0166161309885</v>
+        <v>-349.4993329290479</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-540.3151065801668</v>
+        <v>-531.6033364226136</v>
       </c>
     </row>
     <row r="31">
@@ -2946,12 +2946,10 @@
         <v>-0.048098</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-0.057716</v>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.36</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="100">
@@ -2975,10 +2973,8 @@
       <c r="F100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -3000,12 +2996,10 @@
         <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.272</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>-0.152</v>
       </c>
     </row>
     <row r="102">
@@ -3029,10 +3023,8 @@
       <c r="F102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -3056,10 +3048,8 @@
       <c r="F103" s="3" t="n">
         <v>-0.003901</v>
       </c>
-      <c r="G103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -3081,12 +3071,10 @@
         <v>0.006389</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0.001738</v>
-      </c>
-      <c r="G104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.006</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0.019</v>
       </c>
     </row>
     <row r="105">
@@ -3110,10 +3098,8 @@
       <c r="F105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -3135,12 +3121,10 @@
         <v>0.006389</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.002163</v>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.274099</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>-0.133</v>
       </c>
     </row>
     <row r="107">
@@ -3164,10 +3148,8 @@
       <c r="F107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -3191,10 +3173,8 @@
       <c r="F108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -3218,10 +3198,8 @@
       <c r="F109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -3245,10 +3223,8 @@
       <c r="F110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -3270,12 +3246,10 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.132</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>-0.006</v>
       </c>
     </row>
     <row r="112">
@@ -3299,10 +3273,8 @@
       <c r="F112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -3326,10 +3298,8 @@
       <c r="F113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -3353,10 +3323,8 @@
       <c r="F114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -3380,10 +3348,8 @@
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -3407,10 +3373,8 @@
       <c r="F116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -3434,10 +3398,8 @@
       <c r="F117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -3461,10 +3423,8 @@
       <c r="F118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -3490,12 +3450,10 @@
         </is>
       </c>
       <c r="F119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.132</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>-2.135</v>
       </c>
     </row>
     <row r="120">
@@ -3519,10 +3477,8 @@
       <c r="F120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -3546,10 +3502,8 @@
       <c r="F121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3573,10 +3527,8 @@
       <c r="F122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3600,10 +3552,8 @@
       <c r="F123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3625,12 +3575,10 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="125">
@@ -3652,12 +3600,10 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -3681,10 +3627,8 @@
       <c r="F126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3745,10 +3689,8 @@
       <c r="F128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3774,12 +3716,10 @@
         </is>
       </c>
       <c r="F129" s="3" t="n">
-        <v>0.9112</v>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>3.41</v>
       </c>
     </row>
     <row r="130">
@@ -3808,15 +3748,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F130" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0.546</v>
       </c>
     </row>
     <row r="131">
@@ -3840,10 +3776,8 @@
       <c r="F131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3865,12 +3799,10 @@
         <v>-0.041709</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.851321</v>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.332</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="133">
@@ -3899,15 +3831,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F133" s="3" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0.605</v>
       </c>
     </row>
     <row r="134">
@@ -3929,12 +3857,10 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.132</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>-0.006</v>
       </c>
     </row>
     <row r="135">
@@ -3956,12 +3882,10 @@
         <v>-0.041709</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.059879</v>
-      </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.391</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>-1.239</v>
       </c>
     </row>
   </sheetData>
@@ -3975,7 +3899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6054,34 +5978,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ended December   ended December</t>
+          <t>CASH FLOWS PROVIDED BY (USED IN) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ended December   ended December</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>0.00202</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>0.002023</v>
+          <t>Net profit (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I45" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.36</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="46">
@@ -6092,40 +6026,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>CASH FLOWS PROVIDED BY (USED IN) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Adjustments required to reflect net cash from (used in) operating activities (see Appendix A):</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F46" s="5" t="n">
-        <v>-0.089365</v>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>-0.10767</v>
-      </c>
-      <c r="H46" s="5" t="n">
-        <v>-0.048098</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I46" s="5" t="n">
-        <v>-0.057716</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.163</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>4.597</v>
       </c>
     </row>
     <row r="47">
@@ -6136,17 +6070,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>CASH FLOWS PROVIDED BY (USED IN) OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Receivables and prepaid expenses</t>
+          <t>Net cash provided by (used in) operating activities</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6170,12 +6104,10 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>-0.003901</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.523</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-1.233</v>
       </c>
     </row>
     <row r="48">
@@ -6186,38 +6118,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Purchase of property and equipment</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.003351</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.031005</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>-0.021669</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>0.006389</v>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0.001738</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.132</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.006</v>
       </c>
     </row>
     <row r="49">
@@ -6228,38 +6166,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital item</t>
+          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net cash used by operating activities</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>-1.8e-05</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-0.05836</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>-0.086004</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>-0.041709</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>-0.059879</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Changes in short term deposit</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.588</v>
       </c>
     </row>
     <row r="50">
@@ -6270,12 +6212,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Proceeds from the issuance of shares, net of issuance costs</t>
+          <t>Investment in convertible loan receivable (Note 5)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -6284,24 +6226,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.250945</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n">
-        <v>0.9112</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-2.717</v>
       </c>
     </row>
     <row r="51">
@@ -6312,17 +6258,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -6330,11 +6276,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.250945</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -6342,12 +6292,10 @@
         </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.9112</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.132</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-2.135</v>
       </c>
     </row>
     <row r="52">
@@ -6358,19 +6306,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Issuance of convertible debentures, net of issuance costs (Note 8)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -6381,19 +6325,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n">
-        <v>0.164941</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>-0.041709</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>0.851321</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>3.464</v>
       </c>
     </row>
     <row r="53">
@@ -6404,12 +6352,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning</t>
+          <t>Exercise of warrants</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -6418,22 +6366,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F53" s="5" t="n">
-        <v>-1.8e-05</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0.081622</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>0.246563</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>0.204854</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="54">
@@ -6444,12 +6398,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, ending $</t>
+          <t>Net increase in cash resulting from reverse recapitalization (Note 3)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -6458,22 +6412,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F54" s="5" t="n">
-        <v>0.081622</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.246563</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0.204854</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>1.056175</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="55">
@@ -6484,36 +6444,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cash and cash equivalent consist of the following</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cash held in banks $</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Lease payments</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F55" s="5" t="n">
-        <v>0.081622</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>0.016563</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>0.024854</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.016175</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -6524,15 +6492,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cash and cash equivalent consist of the following</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Guaranteed investment certificates</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Net cash from (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -6543,19 +6515,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>0.18</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" s="5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.059</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>3.41</v>
       </c>
     </row>
     <row r="57">
@@ -6566,36 +6540,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cash and cash equivalent consist of the following</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cash and cash equivalent consist of the following total</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>NET INCREASE (DECREASE) IN CASH AND CASH EQUIVALENTS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.081622</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>0.246563</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>0.204854</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I57" s="5" t="n">
-        <v>1.056175</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.332</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="58">
@@ -6606,19 +6588,15 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Item not involving cash</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Share-based payment</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>EXCHANGE DIFFERENCES ON CASH AND CASH EQUIVALENTS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -6629,23 +6607,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>0.043335</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>0.017</v>
       </c>
     </row>
     <row r="59">
@@ -6656,15 +6632,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Issuance of agent’s options $</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>CASH AND CASH EQUIVALENTS AT BEGINNING OF THE YEAR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -6675,23 +6655,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>0.022415</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>0.546</v>
       </c>
     </row>
     <row r="60">
@@ -6702,15 +6680,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>CASH FLOWS USED IN FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Item not involving cash:</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>CASH AND CASH EQUIVALENTS AT END OF THE YEAR</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -6721,23 +6703,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>0.043335</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="5" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>0.605</v>
       </c>
     </row>
     <row r="61">
@@ -6748,44 +6728,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Increase in cash</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Exchange differences on cash and cash equivalent</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>0.08164</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.164941</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="J61" s="5" t="n">
+        <v>-0.017</v>
       </c>
     </row>
     <row r="62">
@@ -6796,24 +6772,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cash flows from operating activities</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-0.003369</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.089365</v>
+          <t>Changes in deferred taxes, net</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6825,15 +6801,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="5" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="J62" s="5" t="n">
+        <v>-0.167</v>
       </c>
     </row>
     <row r="63">
@@ -6844,22 +6816,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Proceeds from shares issued</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F63" s="5" t="n">
-        <v>0.14</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -6871,15 +6849,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="5" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="J63" s="5" t="n">
+        <v>0.094</v>
       </c>
     </row>
     <row r="64">
@@ -6890,24 +6864,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>-1.8e-05</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0.08164</v>
+          <t>Amortization of discount on convertible debentures (Note 8)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -6924,10 +6898,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J64" s="5" t="n">
+        <v>0.09</v>
       </c>
     </row>
     <row r="65">
@@ -6938,12 +6910,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cash (bank indebtedness), beginning</t>
+          <t>Interest expenses on convertible debenture (Note</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -6952,8 +6924,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" s="5" t="n">
-        <v>-1.8e-05</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6965,15 +6939,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="5" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="66">
@@ -6984,20 +6954,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cash (bank indebtedness), ending $</t>
+          <t>Share-based payment to employees</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>-1.8e-05</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.081622</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -7014,22 +6988,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J66" s="5" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>APPENDIX A</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Revenues 11(a)</t>
+          <t>Listing expenses (non-cash) (Note 3)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -7053,23 +7029,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="5" t="n">
-        <v>9.875</v>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>10.846</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>APPENDIX A</t>
+        </is>
+      </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cost of revenues 11(b)</t>
+          <t>Revaluation of convertible loan receivable (Note 5)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -7093,30 +7075,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="5" t="n">
-        <v>8.226000000000001</v>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="5" t="n">
-        <v>9.766999999999999</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>APPENDIX A</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>GrossProfit</t>
-        </is>
-      </c>
+          <t>Revaluation of loan commitment liability (Note 5)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -7137,27 +7121,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="5" t="n">
-        <v>1.649</v>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="5" t="n">
-        <v>1.079</v>
+        <v>-0.003</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sales and marketing 11(c)</t>
+          <t>convertible loan receivable revaluation (Note 5)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -7181,34 +7167,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>0.656</v>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="5" t="n">
-        <v>1.158</v>
+        <v>0.653</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>General and administrative 11(d)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Lease financing expenses</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -7230,26 +7214,26 @@
         </is>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.326</v>
+        <v>-0.004</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>1.177</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>APPENDIX A</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Other expenses 11(e)</t>
+          <t>APPENDIX A total</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -7274,33 +7258,29 @@
         </is>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.139</v>
+        <v>0.083</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>0.004</v>
+        <v>4.422</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Operating profit (loss)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Decrease in trade receivables</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -7322,29 +7302,33 @@
         </is>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.528</v>
+        <v>0.092</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-1.26</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Listing expenses 3</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Decrease (increase) in other receivables</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -7365,29 +7349,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="5" t="n">
+        <v>0.272</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>3.784</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Financial income 11(f)</t>
+          <t>Increase in related parties payable</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -7411,29 +7393,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="5" t="n">
+        <v>2.059</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.014</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Financial expenses 11(f)</t>
+          <t>Increase in inventory</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7458,29 +7438,33 @@
         </is>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.031</v>
+        <v>-2.195</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0.959</v>
+        <v>-0.743</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Financial expenses (income), net</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Decrease in trade payables</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -7502,26 +7486,26 @@
         </is>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.031</v>
+        <v>0.006</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.945</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Profit (loss) before taxes</t>
+          <t>Decrease (increase) in other payables</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -7546,29 +7530,33 @@
         </is>
       </c>
       <c r="I78" s="5" t="n">
-        <v>0.497</v>
+        <v>-0.154</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>-5.989</v>
+        <v>0.197</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Changes in working capital</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tax expense (benefit) 12</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>Adjustments required to reflect net cash provided by (used in) operating activities</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -7590,33 +7578,29 @@
         </is>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0.137</v>
+        <v>0.163</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.159</v>
+        <v>4.597</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Net profit (loss) and total comprehensive profit (loss) for the year</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -7638,31 +7622,31 @@
         </is>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.36</v>
+        <v>0.01</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>-5.83</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Earnings (loss) per common share (basic and diluted)</t>
+          <t>Interest paid</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7686,33 +7670,29 @@
         </is>
       </c>
       <c r="I81" s="5" t="n">
-        <v>5e-08</v>
+        <v>0.017</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-6.9e-07</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental disclosure of cash flow information</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding (*)</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Taxes paid</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -7734,26 +7714,26 @@
         </is>
       </c>
       <c r="I82" s="5" t="n">
-        <v>7.142857</v>
+        <v>0.158</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>8.388211999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>shares(**)    capital    reserve     reserve    earnings   Total</t>
+          <t>Non cash financing and investing activities</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Balance as of January 1, 2024 7,142,857 (*) - -</t>
+          <t>Right of use assets obtained in exchange for lease liabilities</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -7778,33 +7758,31 @@
         </is>
       </c>
       <c r="I83" s="5" t="n">
-        <v>1.044</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>1.044</v>
+        <v>0.273</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>shares(**)    capital    reserve     reserve    earnings   Total</t>
+          <t>Non cash financing and investing activities</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Net profit for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share-based payment in connection with issuance costs of convertible debentures</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>-</t>
@@ -7825,27 +7803,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="5" t="n">
-        <v>0.36</v>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="5" t="n">
-        <v>0.36</v>
+        <v>0.242</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>shares(**)    capital    reserve     reserve    earnings   Total</t>
+          <t>Non cash financing and investing activities</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2024 7,142,857 (*) - -</t>
+          <t>Conversion of debt into equity (Note 10(b))</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -7869,27 +7849,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n">
-        <v>1.404</v>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="5" t="n">
-        <v>1.404</v>
+        <v>2.463</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Effect of reverse recapitalization transaction</t>
+          <t>a.  Fort Technology Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>(Note 3) 2,378,572 4,168 - -</t>
+          <t>Fort Technology Inc. (formerly Impact Acquisitions Corp.) (the “Company”) was incorporated on December</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -7914,28 +7896,26 @@
         </is>
       </c>
       <c r="I86" s="5" t="n">
-        <v>4.168</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.019</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Effect of reverse recapitalization transaction</t>
+          <t>b.  Fort Products Limited</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Issuance of convertible debentures (Note 8) - - - 185</t>
+          <t>Fort, a private company incorporated under the laws of England and Wales, was established on November</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -7960,28 +7940,26 @@
         </is>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.005</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with</t>
+          <t>d.   Liquidity</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with issuance costs of convertible debentures 128,861 242 - -</t>
+          <t>December</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -8006,53 +7984,43 @@
         </is>
       </c>
       <c r="I88" s="5" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.024</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with</t>
+          <t>ended December   ended December</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Exercise of warrants 11,260 11 - -</t>
+          <t>ended December   ended December</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0.002021</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0.002023</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.011</v>
+        <v>3.1e-05</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -8063,42 +8031,40 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Share-based payment - - 150 -</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F90" s="5" t="n">
+        <v>-0.089365</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-0.10767</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>-0.048098</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>0.15</v>
+        <v>-0.057716</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -8109,20 +8075,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Conversion of debt into equity (Note 10(b)) 1,700,802 2,463 - -</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
+          <t>Receivables and prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -8144,7 +8114,7 @@
         </is>
       </c>
       <c r="I91" s="5" t="n">
-        <v>2.463</v>
+        <v>-0.003901</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -8155,109 +8125,101 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - -</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0.003351</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0.031005</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.021669</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0.006389</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-5.83</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-5.83</v>
+        <v>0.001738</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Share-based payment in connection with</t>
+          <t>Change in non-cash working capital item</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Balance as of December 31, 2025 11,362,352 6,884 150 185</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used by operating activities</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>-1.8e-05</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.05836</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.086004</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.041709</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>2.793</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-4.426</v>
+        <v>-0.059879</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Accounting 6 $</t>
+          <t>Proceeds from the issuance of shares, net of issuance costs</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -8266,21 +8228,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>0.036792</v>
+      <c r="F94" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.250945</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.036842</v>
+        <v>0.9112</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -8291,22 +8251,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8314,21 +8274,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>0.000113</v>
+      <c r="F95" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.250945</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.000263</v>
+        <v>0.9112</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -8339,20 +8297,24 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Filing and Other Fees</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Increase (Decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -8363,16 +8325,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G96" s="5" t="n">
+        <v>0.164941</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.014365</v>
+        <v>-0.041709</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.023423</v>
+        <v>0.851321</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -8383,44 +8343,36 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents, beginning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="5" t="n">
+        <v>-1.8e-05</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.081622</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>-0.006511</v>
+        <v>0.246563</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.008756</v>
+        <v>0.204854</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -8431,44 +8383,36 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Legal</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents, ending $</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F98" s="5" t="n">
+        <v>0.081622</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.246563</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.003339</v>
+        <v>0.204854</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.005944</v>
+        <v>1.056175</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -8479,17 +8423,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash and cash equivalent consist of the following</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Expenses (Income) total</t>
+          <t>Cash held in banks $</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -8498,21 +8442,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="5" t="n">
+        <v>0.081622</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.016563</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.048098</v>
+        <v>0.024854</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.057716</v>
+        <v>0.016175</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -8523,24 +8463,20 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Expenses (Income)</t>
+          <t>Cash and cash equivalent consist of the following</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Guaranteed investment certificates</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -8551,16 +8487,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G100" s="5" t="n">
+        <v>0.23</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.048098</v>
+        <v>0.18</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>-0.057716</v>
+        <v>1.04</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
@@ -8571,40 +8505,36 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common</t>
+          <t>Cash and cash equivalent consist of the following</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalent consist of the following total</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.081622</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.246563</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.204854</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>-1e-08</v>
+        <v>1.056175</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
@@ -8615,34 +8545,46 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>common shares outstanding – basic</t>
+          <t>Item not involving cash</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>1.798356</v>
+          <t>Share-based payment</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>5.249315</v>
-      </c>
-      <c r="H102" s="5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I102" s="5" t="n">
-        <v>7.767213</v>
+        <v>0.043335</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -8653,17 +8595,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 5,800,000 $ 368,530 $ 65,750 $</t>
+          <t>Issuance of agent’s options $</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -8677,16 +8619,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="5" t="n">
-        <v>0.233876</v>
-      </c>
-      <c r="I103" s="5" t="n">
-        <v>-0.200404</v>
+      <c r="G103" s="5" t="n">
+        <v>0.022415</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -8697,24 +8641,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Item not involving cash:</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -8726,13 +8666,17 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.10767</v>
-      </c>
-      <c r="H104" s="5" t="n">
-        <v>-0.048098</v>
-      </c>
-      <c r="I104" s="5" t="n">
-        <v>-4.8098e-05</v>
+        <v>0.043335</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -8743,40 +8687,44 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 5,800,000 368,530 65,750</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>Increase in cash</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H105" s="5" t="n">
-        <v>0.185778</v>
-      </c>
-      <c r="I105" s="5" t="n">
-        <v>-0.248502</v>
+      <c r="F105" s="5" t="n">
+        <v>0.08164</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.164941</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -8787,37 +8735,39 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Cash flows from operating activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Shares issued for cash 20,000,000 1,000,000 -</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>-0.089365</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H106" s="5" t="n">
-        <v>1</v>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -8833,37 +8783,41 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Finder shares issued 2,500,000 125,000 -</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Proceeds from shares issued</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="5" t="n">
+        <v>0.14</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="5" t="n">
-        <v>0.125</v>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -8879,37 +8833,39 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Share issuance costs - (213,800) -</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>-1.8e-05</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.08164</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="5" t="n">
-        <v>-0.2138</v>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -8925,17 +8881,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 28,300,000 $ 1,279,730 $ 65,750 $</t>
+          <t>Cash (bank indebtedness), beginning</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -8944,21 +8900,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="5" t="n">
+        <v>-1.8e-05</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H109" s="5" t="n">
-        <v>1.039262</v>
-      </c>
-      <c r="I109" s="5" t="n">
-        <v>-0.306218</v>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -8969,35 +8927,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Accounting 6 $</t>
+          <t>Cash (bank indebtedness), ending $</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.033532</v>
-      </c>
-      <c r="H110" s="5" t="n">
-        <v>0.036792</v>
+      <c r="E110" s="5" t="n">
+        <v>-1.8e-05</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.081622</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -9016,42 +8974,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bank Charges</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="n">
-        <v>1.8e-05</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>0.000113</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>0.000136</v>
-      </c>
-      <c r="H111" s="5" t="n">
-        <v>0.000113</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Revenues 11(a)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>9.875</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>10.846</v>
       </c>
     </row>
     <row r="112">
@@ -9060,14 +9014,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Filing and Other Fees</t>
+          <t>Cost of revenues 11(b)</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -9076,24 +9026,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F112" s="5" t="n">
-        <v>0.014713</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>0.024039</v>
-      </c>
-      <c r="H112" s="5" t="n">
-        <v>0.014365</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>8.226000000000001</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>9.766999999999999</v>
       </c>
     </row>
     <row r="113">
@@ -9102,19 +9054,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>GrossProfit</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9132,18 +9080,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H113" s="5" t="n">
-        <v>-0.006511</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>1.649</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="114">
@@ -9154,19 +9100,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Legal 6</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Sales and marketing 11(c)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -9177,21 +9119,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G114" s="5" t="n">
-        <v>0.006628</v>
-      </c>
-      <c r="H114" s="5" t="n">
-        <v>0.003339</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>1.158</v>
       </c>
     </row>
     <row r="115">
@@ -9202,15 +9144,19 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Share-based payment 5, 6</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>General and administrative 11(d)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -9221,23 +9167,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G115" s="5" t="n">
-        <v>0.043335</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="5" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>1.177</v>
       </c>
     </row>
     <row r="116">
@@ -9248,42 +9192,40 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Other expenses 11(e)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F116" s="5" t="n">
-        <v>0.089365</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0.10767</v>
-      </c>
-      <c r="H116" s="5" t="n">
-        <v>0.048098</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>0.004</v>
       </c>
     </row>
     <row r="117">
@@ -9294,17 +9236,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Operating profit (loss)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9312,24 +9254,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F117" s="5" t="n">
-        <v>-0.089365</v>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>-0.10767</v>
-      </c>
-      <c r="H117" s="5" t="n">
-        <v>-0.048098</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="118">
@@ -9340,12 +9284,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 2,800,000 $ 140,000 $ - $</t>
+          <t>Listing expenses 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -9359,21 +9303,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G118" s="5" t="n">
-        <v>0.047266</v>
-      </c>
-      <c r="H118" s="5" t="n">
-        <v>-0.092734</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J118" s="5" t="n">
+        <v>3.784</v>
       </c>
     </row>
     <row r="119">
@@ -9384,12 +9330,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Shares issued for cash 3,000,000 300,000 -</t>
+          <t>Financial income 11(f)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9403,8 +9349,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G119" s="5" t="n">
-        <v>0.3</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9416,10 +9364,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J119" s="5" t="n">
+        <v>-0.014</v>
       </c>
     </row>
     <row r="120">
@@ -9430,12 +9376,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Share issuance costs - (71,470) 22,415</t>
+          <t>Financial expenses 11(f)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9449,23 +9395,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G120" s="5" t="n">
-        <v>-0.049055</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I120" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0.959</v>
       </c>
     </row>
     <row r="121">
@@ -9476,12 +9420,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Share-based payment - - 43,335</t>
+          <t>Financial expenses (income), net</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9495,23 +9439,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="5" t="n">
-        <v>0.043335</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I121" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="J121" s="5" t="n">
+        <v>0.945</v>
       </c>
     </row>
     <row r="122">
@@ -9522,12 +9464,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 5,800,000 368,530 65,750</t>
+          <t>Profit (loss) before taxes</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9541,21 +9483,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>0.233876</v>
-      </c>
-      <c r="H122" s="5" t="n">
-        <v>-0.200404</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="5" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="J122" s="5" t="n">
+        <v>-5.989</v>
       </c>
     </row>
     <row r="123">
@@ -9566,12 +9508,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 5,800,000 $ 368,530 $ 65,750 $</t>
+          <t>Tax expense (benefit) 12</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9585,21 +9527,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="5" t="n">
-        <v>0.185778</v>
-      </c>
-      <c r="H123" s="5" t="n">
-        <v>-0.248502</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="5" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="J123" s="5" t="n">
+        <v>-0.159</v>
       </c>
     </row>
     <row r="124">
@@ -9610,40 +9552,44 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Accounting 5 $</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Net profit (loss) and total comprehensive profit (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F124" s="5" t="n">
-        <v>0.013729</v>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>0.033532</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J124" s="5" t="n">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="125">
@@ -9654,22 +9600,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Financing Fees</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Earnings (loss) per common share (basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F125" s="5" t="n">
-        <v>0.01025</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -9681,15 +9633,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I125" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="J125" s="5" t="n">
+        <v>-6.9e-07</v>
       </c>
     </row>
     <row r="126">
@@ -9700,17 +9648,17 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Legal 5</t>
+          <t>Weighted average common shares outstanding (*)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9718,26 +9666,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F126" s="5" t="n">
-        <v>0.05056</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.006628</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="5" t="n">
+        <v>7.142857</v>
+      </c>
+      <c r="J126" s="5" t="n">
+        <v>8.388211999999999</v>
       </c>
     </row>
     <row r="127">
@@ -9748,12 +9696,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares(**)    capital    reserve     reserve    earnings   Total</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Share-based payment 4, 5</t>
+          <t>Balance as of January 1, 2024 7,142,857 (*) - -</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -9767,23 +9715,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G127" s="5" t="n">
-        <v>0.043335</v>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I127" s="5" t="n">
+        <v>1.044</v>
+      </c>
+      <c r="J127" s="5" t="n">
+        <v>1.044</v>
       </c>
     </row>
     <row r="128">
@@ -9794,40 +9740,44 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>shares(**)    capital    reserve     reserve    earnings   Total</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 1 $ - $ - $</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Net profit for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F128" s="5" t="n">
-        <v>-0.003369</v>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>-0.003369</v>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="J128" s="5" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="129">
@@ -9838,12 +9788,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>shares(**)    capital    reserve     reserve    earnings   Total</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cancellation of Incorporation share (1) - -</t>
+          <t>Balance as of December 31, 2024 7,142,857 (*) - -</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -9867,15 +9817,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="5" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>1.404</v>
       </c>
     </row>
     <row r="130">
@@ -9886,12 +9832,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Effect of reverse recapitalization transaction</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Proceeds for shares issued 2,800,000 140,000 -</t>
+          <t>(Note 3) 2,378,572 4,168 - -</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -9900,8 +9846,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F130" s="5" t="n">
-        <v>0.14</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -9913,10 +9861,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="5" t="n">
+        <v>4.168</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -9932,39 +9878,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Effect of reverse recapitalization transaction</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Net Loss - - -</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of convertible debentures (Note 8) - - - 185</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F131" s="5" t="n">
-        <v>-0.089365</v>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>-0.089365</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I131" s="5" t="n">
+        <v>0.185</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -9980,12 +9924,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Share-based payment in connection with</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 2,800,000 140,000 -</t>
+          <t>Share-based payment in connection with issuance costs of convertible debentures 128,861 242 - -</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -9994,21 +9938,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F132" s="5" t="n">
-        <v>0.047266</v>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>-0.092734</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="5" t="n">
+        <v>0.242</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -10024,12 +9970,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Share-based payment in connection with</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Shares issued for cash 3,000,000 300,000 -</t>
+          <t>Exercise of warrants 11,260 11 - -</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -10038,8 +9984,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F133" s="5" t="n">
-        <v>0.3</v>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -10051,10 +9999,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="5" t="n">
+        <v>0.011</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -10070,12 +10016,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Share-based payment in connection with</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Share issuance costs - (71,470) 22,415</t>
+          <t>Share-based payment - - 150 -</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10084,8 +10030,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F134" s="5" t="n">
-        <v>-0.049055</v>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -10097,10 +10045,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I134" s="5" t="n">
+        <v>0.15</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -10116,12 +10062,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Share-based payment in connection with</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Share-based payment - - 43,335</t>
+          <t>Conversion of debt into equity (Note 10(b)) 1,700,802 2,463 - -</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -10130,8 +10076,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F135" s="5" t="n">
-        <v>0.043335</v>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -10143,10 +10091,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="5" t="n">
+        <v>2.463</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -10162,12 +10108,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Share-based payment in connection with</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
+          <t>Net loss for the year - - - -</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10180,26 +10126,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F136" s="5" t="n">
-        <v>-0.10767</v>
-      </c>
-      <c r="G136" s="5" t="n">
-        <v>-0.10767</v>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I136" s="5" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="J136" s="5" t="n">
+        <v>-5.83</v>
       </c>
     </row>
     <row r="137">
@@ -10210,12 +10156,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+          <t>Share-based payment in connection with</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 5,800,000 $ 368,530 $ 65,750 $</t>
+          <t>Balance as of December 31, 2025 11,362,352 6,884 150 185</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -10224,26 +10170,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F137" s="5" t="n">
-        <v>0.233876</v>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>-0.200404</v>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="5" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="J137" s="5" t="n">
+        <v>-4.426</v>
       </c>
     </row>
     <row r="138">
@@ -10254,39 +10200,35 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Legal 5 $</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="n">
-        <v>0.000851</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>0.05056</v>
+          <t>Accounting 6 $</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H138" s="5" t="n">
+        <v>0.036792</v>
+      </c>
+      <c r="I138" s="5" t="n">
+        <v>0.036842</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -10302,35 +10244,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Accounting 5</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" s="5" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>0.013729</v>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H139" s="5" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="I139" s="5" t="n">
+        <v>0.000263</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -10346,39 +10292,35 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E140" s="5" t="n">
-        <v>0.003369</v>
-      </c>
-      <c r="F140" s="5" t="n">
-        <v>0.089365</v>
+          <t>Filing and Other Fees</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H140" s="5" t="n">
+        <v>0.014365</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>0.023423</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -10394,39 +10336,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
+          <t>Interest Income</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E141" s="5" t="n">
-        <v>-0.003369</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>-0.089365</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H141" s="5" t="n">
+        <v>-0.006511</v>
+      </c>
+      <c r="I141" s="5" t="n">
+        <v>-0.008756</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -10442,35 +10384,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common         $                    $ share</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" s="5" t="n">
-        <v>-0.003369</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>-5e-08</v>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H142" s="5" t="n">
+        <v>0.003339</v>
+      </c>
+      <c r="I142" s="5" t="n">
+        <v>0.005944</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -10486,12 +10432,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Shares          Amount             Deficit                 Equity</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Balance January 1, 2020 1 $ - $</t>
+          <t>Expenses (Income) total</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -10510,15 +10456,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H143" s="5" t="n">
+        <v>-0.048098</v>
+      </c>
+      <c r="I143" s="5" t="n">
+        <v>-0.057716</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -10534,12 +10476,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Shares          Amount             Deficit                 Equity</t>
+          <t>Expenses (Income)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Net loss for the year - -</t>
+          <t>Net and comprehensive loss $</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10547,26 +10489,26 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E144" s="5" t="n">
-        <v>-0.003369</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>-0.003369</v>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H144" s="5" t="n">
+        <v>-0.048098</v>
+      </c>
+      <c r="I144" s="5" t="n">
+        <v>-0.057716</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -10582,35 +10524,35 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Shares          Amount             Deficit                 Equity</t>
+          <t>Basic and diluted loss per common</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 1 -</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" s="5" t="n">
-        <v>-0.003369</v>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F145" s="5" t="n">
-        <v>-0.003369</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5e-08</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I145" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -10626,39 +10568,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Shares          Amount             Deficit                 Equity</t>
+          <t>common shares outstanding – basic</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cancellation of Incorporation shares (1) -</t>
+          <t>common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E146" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F146" s="5" t="n">
+        <v>1.798356</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>5.249315</v>
+      </c>
+      <c r="H146" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>7.767213</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -10674,17 +10606,19 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Shares          Amount             Deficit                 Equity</t>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Shares issued 2,800,000 140,000</t>
+          <t>Balance, December 31, 2022 5,800,000 $ 368,530 $ 65,750 $</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>0.14</v>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -10696,15 +10630,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H147" s="5" t="n">
+        <v>0.233876</v>
+      </c>
+      <c r="I147" s="5" t="n">
+        <v>-0.200404</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -10720,37 +10650,2055 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>-0.10767</v>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>-0.048098</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>-4.8098e-05</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 5,800,000 368,530 65,750</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="5" t="n">
+        <v>0.185778</v>
+      </c>
+      <c r="I149" s="5" t="n">
+        <v>-0.248502</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Shares issued for cash 20,000,000 1,000,000 -</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Finder shares issued 2,500,000 125,000 -</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (213,800) -</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>-0.2138</v>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2024 28,300,000 $ 1,279,730 $ 65,750 $</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="5" t="n">
+        <v>1.039262</v>
+      </c>
+      <c r="I153" s="5" t="n">
+        <v>-0.306218</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Accounting 6 $</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.033532</v>
+      </c>
+      <c r="H154" s="5" t="n">
+        <v>0.036792</v>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="F155" s="5" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="H155" s="5" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Filing and Other Fees</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>0.014713</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.024039</v>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>0.014365</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="5" t="n">
+        <v>-0.006511</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Legal 6</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>0.006628</v>
+      </c>
+      <c r="H158" s="5" t="n">
+        <v>0.003339</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Share-based payment 5, 6</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.043335</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="n">
+        <v>0.089365</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.10767</v>
+      </c>
+      <c r="H160" s="5" t="n">
+        <v>0.048098</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="n">
+        <v>-0.089365</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>-0.10767</v>
+      </c>
+      <c r="H161" s="5" t="n">
+        <v>-0.048098</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2021 2,800,000 $ 140,000 $ - $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.047266</v>
+      </c>
+      <c r="H162" s="5" t="n">
+        <v>-0.092734</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Shares issued for cash 3,000,000 300,000 -</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (71,470) 22,415</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>-0.049055</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Share-based payment - - 43,335</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.043335</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 5,800,000 368,530 65,750</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.233876</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>-0.200404</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                   Equity</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2023 5,800,000 $ 368,530 $ 65,750 $</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.185778</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>-0.248502</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Accounting 5 $</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>0.013729</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.033532</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Financing Fees</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>0.01025</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Legal 5</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.006628</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Share-based payment 4, 5</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.043335</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2020 1 $ - $ - $</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Cancellation of Incorporation share (1) - -</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Proceeds for shares issued 2,800,000 140,000 -</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Net Loss - - -</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>-0.089365</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>-0.089365</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2021 2,800,000 140,000 -</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>0.047266</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>-0.092734</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Shares issued for cash 3,000,000 300,000 -</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Share issuance costs - (71,470) 22,415</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="n">
+        <v>-0.049055</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Share-based payment - - 43,335</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="n">
+        <v>0.043335</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="n">
+        <v>-0.10767</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>-0.10767</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Shares        Amount         Option Reserve                  Deficit                (Deficiency)</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2022 5,800,000 $ 368,530 $ 65,750 $</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="n">
+        <v>0.233876</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>-0.200404</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Legal 5 $</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>0.000851</v>
+      </c>
+      <c r="F182" s="5" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Accounting 5</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" s="5" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="F183" s="5" t="n">
+        <v>0.013729</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="n">
+        <v>0.003369</v>
+      </c>
+      <c r="F184" s="5" t="n">
+        <v>0.089365</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="F185" s="5" t="n">
+        <v>-0.089365</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common         $                    $ share</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="F186" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
           <t>Shares          Amount             Deficit                 Equity</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Balance January 1, 2020 1 $ - $</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Shares          Amount             Deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Net loss for the year - -</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="F188" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Shares          Amount             Deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Balance, December 31, 2020 1 -</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="F189" s="5" t="n">
+        <v>-0.003369</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Shares          Amount             Deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Cancellation of Incorporation shares (1) -</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Shares          Amount             Deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Shares issued 2,800,000 140,000</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Shares          Amount             Deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
         <is>
           <t>Balance, December 31, 2021 2,800,000 $ 140,000 $</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" s="5" t="n">
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" s="5" t="n">
         <v>0.047266</v>
       </c>
-      <c r="F148" s="5" t="n">
+      <c r="F192" s="5" t="n">
         <v>-0.092734</v>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
         <is>
           <t>-</t>
         </is>
